--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2019_T3_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2019_T3_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>81</t>
+    <t>75</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>1.632</t>
-  </si>
-  <si>
-    <t>(0.264)</t>
-  </si>
-  <si>
-    <t>7.222</t>
-  </si>
-  <si>
-    <t>(0.891)</t>
-  </si>
-  <si>
-    <t>5.357</t>
-  </si>
-  <si>
-    <t>(1.559)</t>
-  </si>
-  <si>
-    <t>12.730</t>
-  </si>
-  <si>
-    <t>(2.493)</t>
-  </si>
-  <si>
-    <t>1.507</t>
-  </si>
-  <si>
-    <t>(0.202)</t>
-  </si>
-  <si>
-    <t>9.247</t>
-  </si>
-  <si>
-    <t>(1.020)</t>
-  </si>
-  <si>
-    <t>3.664</t>
-  </si>
-  <si>
-    <t>(0.778)</t>
-  </si>
-  <si>
-    <t>0.570</t>
-  </si>
-  <si>
-    <t>(0.144)</t>
-  </si>
-  <si>
-    <t>14.600</t>
-  </si>
-  <si>
-    <t>(2.796)</t>
-  </si>
-  <si>
-    <t>10.524</t>
-  </si>
-  <si>
-    <t>(2.189)</t>
+    <t>1.551</t>
+  </si>
+  <si>
+    <t>(0.238)</t>
+  </si>
+  <si>
+    <t>7.707</t>
+  </si>
+  <si>
+    <t>(0.938)</t>
+  </si>
+  <si>
+    <t>4.604</t>
+  </si>
+  <si>
+    <t>(1.247)</t>
+  </si>
+  <si>
+    <t>11.959</t>
+  </si>
+  <si>
+    <t>(2.297)</t>
+  </si>
+  <si>
+    <t>1.599</t>
+  </si>
+  <si>
+    <t>(0.213)</t>
+  </si>
+  <si>
+    <t>9.933</t>
+  </si>
+  <si>
+    <t>(1.061)</t>
+  </si>
+  <si>
+    <t>3.660</t>
+  </si>
+  <si>
+    <t>(0.822)</t>
+  </si>
+  <si>
+    <t>0.544</t>
+  </si>
+  <si>
+    <t>(0.141)</t>
+  </si>
+  <si>
+    <t>13.466</t>
+  </si>
+  <si>
+    <t>(2.343)</t>
+  </si>
+  <si>
+    <t>10.585</t>
+  </si>
+  <si>
+    <t>(2.316)</t>
   </si>
   <si>
     <t>35</t>
@@ -198,7 +198,7 @@
     <t>(3.558)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.140</t>
-  </si>
-  <si>
-    <t>2.321</t>
-  </si>
-  <si>
-    <t>2.412</t>
-  </si>
-  <si>
-    <t>1.883</t>
-  </si>
-  <si>
-    <t>-0.136</t>
-  </si>
-  <si>
-    <t>0.439</t>
-  </si>
-  <si>
-    <t>-0.283</t>
-  </si>
-  <si>
-    <t>-0.250</t>
-  </si>
-  <si>
-    <t>1.228</t>
-  </si>
-  <si>
-    <t>4.244</t>
+    <t>0.221</t>
+  </si>
+  <si>
+    <t>1.836</t>
+  </si>
+  <si>
+    <t>3.165</t>
+  </si>
+  <si>
+    <t>2.654</t>
+  </si>
+  <si>
+    <t>-0.228</t>
+  </si>
+  <si>
+    <t>-0.248</t>
+  </si>
+  <si>
+    <t>-0.279</t>
+  </si>
+  <si>
+    <t>-0.225</t>
+  </si>
+  <si>
+    <t>2.362</t>
+  </si>
+  <si>
+    <t>4.183</t>
   </si>
 </sst>
 </file>
